--- a/src/tasks.xlsx
+++ b/src/tasks.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\projects\ba\src\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C516AE-E067-4097-A71A-EE6D0FB43D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="21690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -18,10 +24,149 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="42">
+  <si>
+    <t>Was ist mein Teilnamefaktor?</t>
+  </si>
+  <si>
+    <t>Aufgabentyp</t>
+  </si>
+  <si>
+    <t>Aufgabe</t>
+  </si>
+  <si>
+    <t>Notiz</t>
+  </si>
+  <si>
+    <t>mp unklar</t>
+  </si>
+  <si>
+    <t>Was ist mein Teilnamefaktor von meinem Verbrauch?</t>
+  </si>
+  <si>
+    <t>Was ist mein Teilnamefaktor von meinem Erzeugerzählpunkt?</t>
+  </si>
+  <si>
+    <t>mp3</t>
+  </si>
+  <si>
+    <t>ohne _</t>
+  </si>
+  <si>
+    <t>Was ist mein Teilnamefaktor von mp1</t>
+  </si>
+  <si>
+    <t>Gib mir den Teilnamefaktor von mp_2</t>
+  </si>
+  <si>
+    <t>Welchen Teilnamefaktor habe ich bei mp_3?</t>
+  </si>
+  <si>
+    <t>Wie viel verbrauche ich gerade?</t>
+  </si>
+  <si>
+    <t>Wie viel verbraucht mp_1 gerade?</t>
+  </si>
+  <si>
+    <t>Wie viel verbraucht mp2 gerade?</t>
+  </si>
+  <si>
+    <t>Wie viel erzeuge ich gerade?</t>
+  </si>
+  <si>
+    <t>Wie viel erzeugt mp_3 gerade?</t>
+  </si>
+  <si>
+    <t>Wie viel verbraucht mp_3 gerade?</t>
+  </si>
+  <si>
+    <t>kein Verbraucherzählpunkt</t>
+  </si>
+  <si>
+    <t>Wie viel erzeugt mp_1 gerade?</t>
+  </si>
+  <si>
+    <t>kein Erzeugerzählpunkt</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Tehma</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>Welchen Teilnamefaktor habe ich?</t>
+  </si>
+  <si>
+    <t>Teilnamefaktor mp1?</t>
+  </si>
+  <si>
+    <t>Wie viel nehme ich mit mp_2 an der Energiegemeinschaft teil?</t>
+  </si>
+  <si>
+    <t>Gib mir den Teilnamefaktor aller meiner Verbraucherzählpunkte.</t>
+  </si>
+  <si>
+    <t>Gib mir den aktuellen Verbrauch aller meine Verbraucherzählpunkte.</t>
+  </si>
+  <si>
+    <t>Wie viel ezeugt mp_1 jetzt gerade?</t>
+  </si>
+  <si>
+    <t>Was viel verbraucht mein Zählpunkt mp_3 gerade?</t>
+  </si>
+  <si>
+    <t>PF</t>
+  </si>
+  <si>
+    <t>MG_eg</t>
+  </si>
+  <si>
+    <t>MC_eg</t>
+  </si>
+  <si>
+    <t>Wie viel hat meine Energiegemeinschaft letzte Woche verbraucht?</t>
+  </si>
+  <si>
+    <t>Gib mir den Gesamtverbrauch meiner Energiegemeinschaft letzten Monat.</t>
+  </si>
+  <si>
+    <t>Zeig mir den Verbrauch meiner Energiegemeinschaft letzte Woche.</t>
+  </si>
+  <si>
+    <t>Was ist der niedrigste Verbrauch meiner Energiegemeinschaft?</t>
+  </si>
+  <si>
+    <t>Direkte Informationsabfrage</t>
+  </si>
+  <si>
+    <t>Einfache Datenverarbeitung</t>
+  </si>
+  <si>
+    <t>Komplexe Datenverarbeitung</t>
+  </si>
+  <si>
+    <t>nicht unterstützt</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,11 +194,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +477,777 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="70.90625" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C101">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>